--- a/processed-data/00_project_prep/05_pathology/LFF_pathtab.xlsx
+++ b/processed-data/00_project_prep/05_pathology/LFF_pathtab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmulvey/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/00_project_prep/05_pathology/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC91DA4-2612-844A-9C11-7B9F953DA1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{88C91879-4083-DB47-85BA-10F7A70440B2}"/>
+    <workbookView xWindow="2200" yWindow="1040" windowWidth="28040" windowHeight="17440" xr2:uid="{88C91879-4083-DB47-85BA-10F7A70440B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
